--- a/Stundenliste_neu.xlsx
+++ b/Stundenliste_neu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VR1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{375F90E3-16D1-46E3-952B-CC44DAF9CE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19FABA60-8916-480A-B67C-E756A852C410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20625" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="66">
   <si>
     <t>Tag</t>
   </si>
@@ -225,6 +225,15 @@
   </si>
   <si>
     <t>Server Besprechung</t>
+  </si>
+  <si>
+    <t>Fehlerbehebung (Debugging)</t>
+  </si>
+  <si>
+    <t>Objekte</t>
+  </si>
+  <si>
+    <t>neue Objekte hinzugefügt</t>
   </si>
 </sst>
 </file>
@@ -324,7 +333,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -358,27 +367,12 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Prozent" xfId="1" builtinId="5"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="17">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="h:mm"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -462,6 +456,20 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="h:mm"/>
     </dxf>
     <dxf>
       <font>
@@ -741,7 +749,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.68256578947368074</c:v>
+                  <c:v>0.73464912280701367</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -941,7 +949,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.57017543859648823</c:v>
+                  <c:v>0.60581140350876872</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1849,8 +1857,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD71F5EC-BCBD-4D95-9F21-060EF7779827}" name="Stundenliste" displayName="Stundenliste" ref="A1:G53" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:G53" xr:uid="{730AE997-56E9-481C-8C9C-45C7D9E3EFFC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD71F5EC-BCBD-4D95-9F21-060EF7779827}" name="Stundenliste" displayName="Stundenliste" ref="A1:G56" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:G56" xr:uid="{730AE997-56E9-481C-8C9C-45C7D9E3EFFC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G41">
     <sortCondition ref="B1:B41"/>
   </sortState>
@@ -1862,10 +1870,10 @@
     <tableColumn id="3" xr3:uid="{8264A4E0-F28F-4A0D-A490-C90DCCB13F8E}" name="Tätigkeit/Info" dataDxfId="12"/>
     <tableColumn id="4" xr3:uid="{FE347096-2316-4A4F-8E95-6B08EDE9030A}" name="Von" dataDxfId="11"/>
     <tableColumn id="5" xr3:uid="{DF9965FF-51AE-44CD-90F9-60C1127D4458}" name="Bis" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{71889B4E-2C0D-4CC7-AB39-54AAA30FF7DC}" name="Stunden" dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{71889B4E-2C0D-4CC7-AB39-54AAA30FF7DC}" name="Stunden" dataDxfId="9">
       <calculatedColumnFormula>IF(E2&gt;D2,E2-D2,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D2-E2),""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{37DB6F7E-AF9C-40D4-A31C-91C6CFAF5E2F}" name="Wer" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{37DB6F7E-AF9C-40D4-A31C-91C6CFAF5E2F}" name="Wer" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1876,17 +1884,17 @@
   <autoFilter ref="L2:Q6" xr:uid="{028D3482-62D4-45D7-85FA-8EC2E4DDD78D}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9B6AAEA3-668A-4353-A33E-0D79279FD064}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{DF593358-143C-4B61-887F-2E7A8967BB61}" name="Stunden" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{48C02AA9-4970-411A-A4BA-20AFF4C20E61}" name="Minuten" dataDxfId="7">
+    <tableColumn id="2" xr3:uid="{DF593358-143C-4B61-887F-2E7A8967BB61}" name="Stunden" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{48C02AA9-4970-411A-A4BA-20AFF4C20E61}" name="Minuten" dataDxfId="6">
       <calculatedColumnFormula>Tabelle2[[#This Row],[Stunden]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{FBD2B55A-1785-4AEE-A362-0CDA5F4271CA}" name="Stunden2" dataDxfId="6">
+    <tableColumn id="4" xr3:uid="{FBD2B55A-1785-4AEE-A362-0CDA5F4271CA}" name="Stunden2" dataDxfId="5">
       <calculatedColumnFormula>Tabelle2[[#This Row],[Minuten]]/60</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{43C88CC5-3A35-4698-8EA5-94C339438E12}" name="Prozent" dataDxfId="5">
+    <tableColumn id="5" xr3:uid="{43C88CC5-3A35-4698-8EA5-94C339438E12}" name="Prozent" dataDxfId="4">
       <calculatedColumnFormula>(O3/180)*100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{6AA6588C-B2BB-4A64-8166-D31634AA0806}" name="Spalte1" dataDxfId="4">
+    <tableColumn id="6" xr3:uid="{6AA6588C-B2BB-4A64-8166-D31634AA0806}" name="Spalte1" dataDxfId="3">
       <calculatedColumnFormula>P3*1421.05263157894</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1895,11 +1903,11 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8B5F2195-23C3-4CB7-A5D3-21B8075D8571}" name="Tabelle5" displayName="Tabelle5" ref="I2:J11" totalsRowShown="0" dataDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8B5F2195-23C3-4CB7-A5D3-21B8075D8571}" name="Tabelle5" displayName="Tabelle5" ref="I2:J11" totalsRowShown="0" dataDxfId="2">
   <autoFilter ref="I2:J11" xr:uid="{8B5F2195-23C3-4CB7-A5D3-21B8075D8571}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5F655F81-B105-43EE-8AB9-3B34703E1464}" name="Name" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{B0F8400B-CC18-431B-B826-95EE145FC5C8}" name="Zeit" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{5F655F81-B105-43EE-8AB9-3B34703E1464}" name="Name" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{B0F8400B-CC18-431B-B826-95EE145FC5C8}" name="Zeit" dataDxfId="0">
       <calculatedColumnFormula>SUMIF(Stundenliste[Wer],I3,Stundenliste[Stunden])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2205,7 +2213,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{730198CE-52B5-4F02-9B4B-1774B163D30B}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:Q56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -2326,23 +2334,23 @@
       </c>
       <c r="M3" s="11">
         <f>SUM(J4,J7,J8,J11)</f>
-        <v>5.1875</v>
+        <v>5.583333333333333</v>
       </c>
       <c r="N3" s="18">
         <f>M3</f>
-        <v>5.1875</v>
+        <v>5.583333333333333</v>
       </c>
       <c r="O3" s="18">
         <f>N3/60</f>
-        <v>8.6458333333333331E-2</v>
+        <v>9.3055555555555544E-2</v>
       </c>
       <c r="P3" s="22">
         <f t="shared" ref="P3:P6" si="1">(O3/180)*100</f>
-        <v>4.8032407407407406E-2</v>
+        <v>5.1697530864197531E-2</v>
       </c>
       <c r="Q3" s="21">
         <f>(P3*1421.05263157894)/100</f>
-        <v>0.68256578947368074</v>
+        <v>0.73464912280701367</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -2374,7 +2382,7 @@
       </c>
       <c r="J4" s="10">
         <f>SUMIF(Stundenliste[Wer],I4,Stundenliste[Stunden])</f>
-        <v>1.25</v>
+        <v>1.375</v>
       </c>
       <c r="L4" t="s">
         <v>11</v>
@@ -2436,23 +2444,23 @@
       </c>
       <c r="M5" s="11">
         <f>SUM(J3,J7,J9,J11)</f>
-        <v>4.333333333333333</v>
+        <v>4.6041666666666661</v>
       </c>
       <c r="N5" s="18">
         <f t="shared" si="2"/>
-        <v>4.333333333333333</v>
+        <v>4.6041666666666661</v>
       </c>
       <c r="O5" s="18">
         <f t="shared" si="3"/>
-        <v>7.2222222222222215E-2</v>
+        <v>7.6736111111111102E-2</v>
       </c>
       <c r="P5" s="22">
         <f t="shared" si="1"/>
-        <v>4.0123456790123455E-2</v>
+        <v>4.2631172839506168E-2</v>
       </c>
       <c r="Q5" s="21">
         <f t="shared" si="4"/>
-        <v>0.57017543859648823</v>
+        <v>0.60581140350876872</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -2527,11 +2535,11 @@
       </c>
       <c r="J7" s="10">
         <f>SUMIF(Stundenliste[Wer],I7,Stundenliste[Stunden])</f>
-        <v>0.49999999999999989</v>
+        <v>0.77083333333333326</v>
       </c>
       <c r="M7" s="15">
-        <f>SUM(F2:F53)</f>
-        <v>6.4236111111111134</v>
+        <f>SUM(F2:F56)</f>
+        <v>6.8194444444444464</v>
       </c>
       <c r="N7">
         <v>180</v>
@@ -2570,7 +2578,7 @@
       </c>
       <c r="M8" s="16">
         <f>TEXT(M7,"[h]")+TEXT(M7,"mm")/60</f>
-        <v>154.16666666666666</v>
+        <v>163.66666666666666</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -3546,14 +3554,14 @@
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="23" t="str">
+      <c r="A47" s="2" t="str">
         <f t="shared" ref="A47:A49" si="6">IF(ISNUMBER(B47),LEFT(TEXT(B47,"TTTT"),2)&amp;".","")</f>
         <v>Sa.</v>
       </c>
       <c r="B47" s="3">
         <v>46067</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C47" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D47" s="4">
@@ -3571,14 +3579,14 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="23" t="str">
+      <c r="A48" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Fr.</v>
       </c>
       <c r="B48" s="3">
         <v>46073</v>
       </c>
-      <c r="C48" s="23" t="s">
+      <c r="C48" s="2" t="s">
         <v>58</v>
       </c>
       <c r="D48" s="4">
@@ -3596,14 +3604,14 @@
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="23" t="str">
+      <c r="A49" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Sa.</v>
       </c>
       <c r="B49" s="3">
         <v>46074</v>
       </c>
-      <c r="C49" s="23" t="s">
+      <c r="C49" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D49" s="4">
@@ -3621,14 +3629,14 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="23" t="str">
+      <c r="A50" s="2" t="str">
         <f>IF(ISNUMBER(B50),LEFT(TEXT(B50,"TTTT"),2)&amp;".","")</f>
         <v>Di.</v>
       </c>
       <c r="B50" s="3">
         <v>46077</v>
       </c>
-      <c r="C50" s="23" t="s">
+      <c r="C50" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D50" s="4">
@@ -3646,14 +3654,14 @@
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="23" t="str">
+      <c r="A51" s="2" t="str">
         <f>IF(ISNUMBER(B51),LEFT(TEXT(B51,"TTTT"),2)&amp;".","")</f>
-        <v>Sa.</v>
+        <v>Fr.</v>
       </c>
       <c r="B51" s="3">
-        <v>46081</v>
-      </c>
-      <c r="C51" s="23" t="s">
+        <v>46080</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>61</v>
       </c>
       <c r="D51" s="4">
@@ -3671,14 +3679,14 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="23" t="str">
+      <c r="A52" s="2" t="str">
         <f>IF(ISNUMBER(B52),LEFT(TEXT(B52,"TTTT"),2)&amp;".","")</f>
-        <v>Sa.</v>
+        <v>Fr.</v>
       </c>
       <c r="B52" s="3">
-        <v>46081</v>
-      </c>
-      <c r="C52" s="23" t="s">
+        <v>46080</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D52" s="4">
@@ -3696,19 +3704,94 @@
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="23" t="str">
+      <c r="A53" s="2" t="str">
         <f>IF(ISNUMBER(B53),LEFT(TEXT(B53,"TTTT"),2)&amp;".","")</f>
+        <v>Fr.</v>
+      </c>
+      <c r="B53" s="3">
+        <v>46080</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D53" s="4">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="E53" s="4">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F53" s="5">
+        <f>IF(E53&gt;D53,E53-D53,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D53-E53),""))</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="str">
+        <f t="shared" ref="A54:A56" si="7">IF(ISNUMBER(B54),LEFT(TEXT(B54,"TTTT"),2)&amp;".","")</f>
+        <v>Fr.</v>
+      </c>
+      <c r="B54" s="3">
+        <v>46080</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D54" s="4">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="E54" s="4">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F54" s="5">
+        <f>IF(E54&gt;D54,E54-D54,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D54-E54),""))</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>Sa.</v>
+      </c>
+      <c r="B55" s="3">
+        <v>46081</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D55" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E55" s="4">
+        <v>0.6875</v>
+      </c>
+      <c r="F55" s="5">
+        <f>IF(E55&gt;D55,E55-D55,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D55-E55),""))</f>
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="str">
+        <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="23"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="5" t="str">
-        <f>IF(E53&gt;D53,E53-D53,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D53-E53),""))</f>
+      <c r="B56" s="3"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="5" t="str">
+        <f>IF(E56&gt;D56,E56-D56,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D56-E56),""))</f>
         <v/>
       </c>
-      <c r="G53" s="2"/>
+      <c r="G56" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/Stundenliste_neu.xlsx
+++ b/Stundenliste_neu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VR1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19FABA60-8916-480A-B67C-E756A852C410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75AF9DA1-F460-43B9-B3CA-C70D539D41C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20625" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="77">
   <si>
     <t>Tag</t>
   </si>
@@ -234,6 +234,39 @@
   </si>
   <si>
     <t>neue Objekte hinzugefügt</t>
+  </si>
+  <si>
+    <t>Unity Download + Setup</t>
+  </si>
+  <si>
+    <t>Projekt importiert und erste Szene erstellt</t>
+  </si>
+  <si>
+    <t>Erste Fehler behoben, Arbeit an der Szene</t>
+  </si>
+  <si>
+    <t>Szene für ToT erstellt, Terrain modelliert</t>
+  </si>
+  <si>
+    <t>Terrain texturiert, Materials erstellt</t>
+  </si>
+  <si>
+    <t>Terrain finished, Fehler behoben</t>
+  </si>
+  <si>
+    <t>Fehlerbehebung für ToT</t>
+  </si>
+  <si>
+    <t>Arbeit an Szenen, Fehlerbehebung</t>
+  </si>
+  <si>
+    <t>Tür fertig gestellt, Fehler behoben, Animationen</t>
+  </si>
+  <si>
+    <t>Teleportation mit Gesten</t>
+  </si>
+  <si>
+    <t>Handtracking</t>
   </si>
 </sst>
 </file>
@@ -333,7 +366,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -367,6 +400,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Prozent" xfId="1" builtinId="5"/>
@@ -749,7 +783,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.73464912280701367</c:v>
+                  <c:v>0.76754385964911886</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -849,7 +883,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.46418128654970525</c:v>
+                  <c:v>0.5957602339181256</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -949,7 +983,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.60581140350876872</c:v>
+                  <c:v>0.65515350877192646</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1857,8 +1891,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD71F5EC-BCBD-4D95-9F21-060EF7779827}" name="Stundenliste" displayName="Stundenliste" ref="A1:G56" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:G56" xr:uid="{730AE997-56E9-481C-8C9C-45C7D9E3EFFC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD71F5EC-BCBD-4D95-9F21-060EF7779827}" name="Stundenliste" displayName="Stundenliste" ref="A1:G66" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:G66" xr:uid="{730AE997-56E9-481C-8C9C-45C7D9E3EFFC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G41">
     <sortCondition ref="B1:B41"/>
   </sortState>
@@ -2213,7 +2247,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{730198CE-52B5-4F02-9B4B-1774B163D30B}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:Q56"/>
+  <dimension ref="A1:Q66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -2327,30 +2361,30 @@
       </c>
       <c r="J3" s="10">
         <f>SUMIF(Stundenliste[Wer],I3,Stundenliste[Stunden])</f>
-        <v>1.145833333333333</v>
+        <v>1.520833333333333</v>
       </c>
       <c r="L3" t="s">
         <v>10</v>
       </c>
       <c r="M3" s="11">
         <f>SUM(J4,J7,J8,J11)</f>
-        <v>5.583333333333333</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="N3" s="18">
         <f>M3</f>
-        <v>5.583333333333333</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="O3" s="18">
         <f>N3/60</f>
-        <v>9.3055555555555544E-2</v>
+        <v>9.7222222222222224E-2</v>
       </c>
       <c r="P3" s="22">
         <f t="shared" ref="P3:P6" si="1">(O3/180)*100</f>
-        <v>5.1697530864197531E-2</v>
+        <v>5.401234567901235E-2</v>
       </c>
       <c r="Q3" s="21">
         <f>(P3*1421.05263157894)/100</f>
-        <v>0.73464912280701367</v>
+        <v>0.76754385964911886</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -2382,30 +2416,30 @@
       </c>
       <c r="J4" s="10">
         <f>SUMIF(Stundenliste[Wer],I4,Stundenliste[Stunden])</f>
-        <v>1.375</v>
+        <v>1.625</v>
       </c>
       <c r="L4" t="s">
         <v>11</v>
       </c>
       <c r="M4" s="11">
         <f>SUM(J5,J8,J9,J11)</f>
-        <v>3.5277777777777781</v>
+        <v>4.5277777777777777</v>
       </c>
       <c r="N4" s="18">
         <f t="shared" ref="N4:N5" si="2">M4</f>
-        <v>3.5277777777777781</v>
+        <v>4.5277777777777777</v>
       </c>
       <c r="O4" s="18">
         <f t="shared" ref="O4:O5" si="3">N4/60</f>
-        <v>5.8796296296296305E-2</v>
+        <v>7.5462962962962968E-2</v>
       </c>
       <c r="P4" s="22">
         <f t="shared" si="1"/>
-        <v>3.2664609053497946E-2</v>
+        <v>4.1923868312757205E-2</v>
       </c>
       <c r="Q4" s="21">
         <f t="shared" ref="Q4:Q5" si="4">(P4*1421.05263157894)/100</f>
-        <v>0.46418128654970525</v>
+        <v>0.5957602339181256</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -2437,30 +2471,30 @@
       </c>
       <c r="J5" s="10">
         <f>SUMIF(Stundenliste[Wer],I5,Stundenliste[Stunden])</f>
-        <v>9.0277777777778123E-2</v>
+        <v>1.0902777777777779</v>
       </c>
       <c r="L5" t="s">
         <v>9</v>
       </c>
       <c r="M5" s="11">
         <f>SUM(J3,J7,J9,J11)</f>
-        <v>4.6041666666666661</v>
+        <v>4.9791666666666661</v>
       </c>
       <c r="N5" s="18">
         <f t="shared" si="2"/>
-        <v>4.6041666666666661</v>
+        <v>4.9791666666666661</v>
       </c>
       <c r="O5" s="18">
         <f t="shared" si="3"/>
-        <v>7.6736111111111102E-2</v>
+        <v>8.2986111111111108E-2</v>
       </c>
       <c r="P5" s="22">
         <f t="shared" si="1"/>
-        <v>4.2631172839506168E-2</v>
+        <v>4.6103395061728392E-2</v>
       </c>
       <c r="Q5" s="21">
         <f t="shared" si="4"/>
-        <v>0.60581140350876872</v>
+        <v>0.65515350877192646</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -2538,8 +2572,8 @@
         <v>0.77083333333333326</v>
       </c>
       <c r="M7" s="15">
-        <f>SUM(F2:F56)</f>
-        <v>6.8194444444444464</v>
+        <f>SUM(F2:F66)</f>
+        <v>8.4444444444444464</v>
       </c>
       <c r="N7">
         <v>180</v>
@@ -2578,7 +2612,7 @@
       </c>
       <c r="M8" s="16">
         <f>TEXT(M7,"[h]")+TEXT(M7,"mm")/60</f>
-        <v>163.66666666666666</v>
+        <v>202.66666666666666</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -3781,17 +3815,277 @@
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="B56" s="3"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="5" t="str">
+        <v>Mo.</v>
+      </c>
+      <c r="B56" s="3">
+        <v>45957</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D56" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E56" s="4">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F56" s="5">
         <f>IF(E56&gt;D56,E56-D56,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D56-E56),""))</f>
-        <v/>
-      </c>
-      <c r="G56" s="2"/>
+        <v>0.12499999999999994</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="23" t="str">
+        <f t="shared" ref="A57:A58" si="8">IF(ISNUMBER(B57),LEFT(TEXT(B57,"TTTT"),2)&amp;".","")</f>
+        <v>Mi.</v>
+      </c>
+      <c r="B57" s="3">
+        <v>45959</v>
+      </c>
+      <c r="C57" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D57" s="4">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E57" s="4">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F57" s="5">
+        <f>IF(E57&gt;D57,E57-D57,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D57-E57),""))</f>
+        <v>0.16666666666666674</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>Do.</v>
+      </c>
+      <c r="B58" s="3">
+        <v>45960</v>
+      </c>
+      <c r="C58" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D58" s="4">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E58" s="4">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F58" s="5">
+        <f>IF(E58&gt;D58,E58-D58,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D58-E58),""))</f>
+        <v>8.3333333333333259E-2</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="23" t="str">
+        <f>IF(ISNUMBER(B59),LEFT(TEXT(B59,"TTTT"),2)&amp;".","")</f>
+        <v>Sa.</v>
+      </c>
+      <c r="B59" s="3">
+        <v>45962</v>
+      </c>
+      <c r="C59" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D59" s="4">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E59" s="4">
+        <v>0.875</v>
+      </c>
+      <c r="F59" s="5">
+        <f>IF(E59&gt;D59,E59-D59,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D59-E59),""))</f>
+        <v>8.333333333333337E-2</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="23" t="str">
+        <f>IF(ISNUMBER(B60),LEFT(TEXT(B60,"TTTT"),2)&amp;".","")</f>
+        <v>So.</v>
+      </c>
+      <c r="B60" s="3">
+        <v>45963</v>
+      </c>
+      <c r="C60" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D60" s="4">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E60" s="4">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F60" s="5">
+        <f>IF(E60&gt;D60,E60-D60,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D60-E60),""))</f>
+        <v>8.3333333333333259E-2</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="23" t="str">
+        <f>IF(ISNUMBER(B61),LEFT(TEXT(B61,"TTTT"),2)&amp;".","")</f>
+        <v>Mi.</v>
+      </c>
+      <c r="B61" s="3">
+        <v>45980</v>
+      </c>
+      <c r="C61" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D61" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="E61" s="4">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F61" s="5">
+        <f>IF(E61&gt;D61,E61-D61,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D61-E61),""))</f>
+        <v>8.3333333333333259E-2</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="23" t="str">
+        <f>IF(ISNUMBER(B62),LEFT(TEXT(B62,"TTTT"),2)&amp;".","")</f>
+        <v>Do.</v>
+      </c>
+      <c r="B62" s="3">
+        <v>45974</v>
+      </c>
+      <c r="C62" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D62" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="E62" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F62" s="5">
+        <f>IF(E62&gt;D62,E62-D62,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D62-E62),""))</f>
+        <v>0.125</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="23" t="str">
+        <f>IF(ISNUMBER(B63),LEFT(TEXT(B63,"TTTT"),2)&amp;".","")</f>
+        <v>So.</v>
+      </c>
+      <c r="B63" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C63" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="D63" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E63" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F63" s="5">
+        <f>IF(E63&gt;D63,E63-D63,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D63-E63),""))</f>
+        <v>0.25000000000000006</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="23" t="str">
+        <f>IF(ISNUMBER(B64),LEFT(TEXT(B64,"TTTT"),2)&amp;".","")</f>
+        <v>So.</v>
+      </c>
+      <c r="B64" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C64" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D64" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E64" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F64" s="5">
+        <f>IF(E64&gt;D64,E64-D64,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D64-E64),""))</f>
+        <v>0.25000000000000006</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="23" t="str">
+        <f>IF(ISNUMBER(B65),LEFT(TEXT(B65,"TTTT"),2)&amp;".","")</f>
+        <v>So.</v>
+      </c>
+      <c r="B65" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C65" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="D65" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E65" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F65" s="5">
+        <f>IF(E65&gt;D65,E65-D65,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D65-E65),""))</f>
+        <v>0.25000000000000006</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="23" t="str">
+        <f>IF(ISNUMBER(B66),LEFT(TEXT(B66,"TTTT"),2)&amp;".","")</f>
+        <v>So.</v>
+      </c>
+      <c r="B66" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C66" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D66" s="4">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E66" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F66" s="5">
+        <f>IF(E66&gt;D66,E66-D66,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D66-E66),""))</f>
+        <v>0.125</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -3806,20 +4100,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3967,6 +4261,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A879EED-63D4-4BD6-ABDC-8DEB19CAAEDF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57E083A2-B59E-4178-BBDB-6F72551558F7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -3980,14 +4282,6 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="becce21f-4543-4ee3-84d8-746b4cf7c34b"/>
     <ds:schemaRef ds:uri="d9f85066-e658-4e34-914c-f198c2427564"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A879EED-63D4-4BD6-ABDC-8DEB19CAAEDF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Stundenliste_neu.xlsx
+++ b/Stundenliste_neu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VR1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anwender\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75AF9DA1-F460-43B9-B3CA-C70D539D41C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532E3A77-40FA-4C1B-A6A5-C26A30555A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20625" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="83">
   <si>
     <t>Tag</t>
   </si>
@@ -267,6 +267,24 @@
   </si>
   <si>
     <t>Handtracking</t>
+  </si>
+  <si>
+    <t>PC-Server Setup</t>
+  </si>
+  <si>
+    <t>PC-Server Kaput</t>
+  </si>
+  <si>
+    <t>Diplo Unity Basics</t>
+  </si>
+  <si>
+    <t>Tür beschrieben</t>
+  </si>
+  <si>
+    <t>Gegenstand werfen + Code</t>
+  </si>
+  <si>
+    <t>PC-Server repariert</t>
   </si>
 </sst>
 </file>
@@ -783,7 +801,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.76754385964911886</c:v>
+                  <c:v>0.81688596491227661</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -883,7 +901,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.5957602339181256</c:v>
+                  <c:v>0.61220760233917815</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -983,7 +1001,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.65515350877192646</c:v>
+                  <c:v>0.6716008771929789</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1891,8 +1909,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD71F5EC-BCBD-4D95-9F21-060EF7779827}" name="Stundenliste" displayName="Stundenliste" ref="A1:G66" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:G66" xr:uid="{730AE997-56E9-481C-8C9C-45C7D9E3EFFC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD71F5EC-BCBD-4D95-9F21-060EF7779827}" name="Stundenliste" displayName="Stundenliste" ref="A1:G73" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:G73" xr:uid="{730AE997-56E9-481C-8C9C-45C7D9E3EFFC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G41">
     <sortCondition ref="B1:B41"/>
   </sortState>
@@ -2247,7 +2265,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{730198CE-52B5-4F02-9B4B-1774B163D30B}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -2368,23 +2386,23 @@
       </c>
       <c r="M3" s="11">
         <f>SUM(J4,J7,J8,J11)</f>
-        <v>5.833333333333333</v>
+        <v>6.2083333333333339</v>
       </c>
       <c r="N3" s="18">
         <f>M3</f>
-        <v>5.833333333333333</v>
+        <v>6.2083333333333339</v>
       </c>
       <c r="O3" s="18">
         <f>N3/60</f>
-        <v>9.7222222222222224E-2</v>
+        <v>0.10347222222222223</v>
       </c>
       <c r="P3" s="22">
         <f t="shared" ref="P3:P6" si="1">(O3/180)*100</f>
-        <v>5.401234567901235E-2</v>
+        <v>5.7484567901234573E-2</v>
       </c>
       <c r="Q3" s="21">
         <f>(P3*1421.05263157894)/100</f>
-        <v>0.76754385964911886</v>
+        <v>0.81688596491227661</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -2416,30 +2434,30 @@
       </c>
       <c r="J4" s="10">
         <f>SUMIF(Stundenliste[Wer],I4,Stundenliste[Stunden])</f>
-        <v>1.625</v>
+        <v>1.8750000000000004</v>
       </c>
       <c r="L4" t="s">
         <v>11</v>
       </c>
       <c r="M4" s="11">
         <f>SUM(J5,J8,J9,J11)</f>
-        <v>4.5277777777777777</v>
+        <v>4.6527777777777777</v>
       </c>
       <c r="N4" s="18">
         <f t="shared" ref="N4:N5" si="2">M4</f>
-        <v>4.5277777777777777</v>
+        <v>4.6527777777777777</v>
       </c>
       <c r="O4" s="18">
         <f t="shared" ref="O4:O5" si="3">N4/60</f>
-        <v>7.5462962962962968E-2</v>
+        <v>7.7546296296296294E-2</v>
       </c>
       <c r="P4" s="22">
         <f t="shared" si="1"/>
-        <v>4.1923868312757205E-2</v>
+        <v>4.3081275720164611E-2</v>
       </c>
       <c r="Q4" s="21">
         <f t="shared" ref="Q4:Q5" si="4">(P4*1421.05263157894)/100</f>
-        <v>0.5957602339181256</v>
+        <v>0.61220760233917815</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -2478,23 +2496,23 @@
       </c>
       <c r="M5" s="11">
         <f>SUM(J3,J7,J9,J11)</f>
-        <v>4.9791666666666661</v>
+        <v>5.1041666666666661</v>
       </c>
       <c r="N5" s="18">
         <f t="shared" si="2"/>
-        <v>4.9791666666666661</v>
+        <v>5.1041666666666661</v>
       </c>
       <c r="O5" s="18">
         <f t="shared" si="3"/>
-        <v>8.2986111111111108E-2</v>
+        <v>8.5069444444444434E-2</v>
       </c>
       <c r="P5" s="22">
         <f t="shared" si="1"/>
-        <v>4.6103395061728392E-2</v>
+        <v>4.7260802469135797E-2</v>
       </c>
       <c r="Q5" s="21">
         <f t="shared" si="4"/>
-        <v>0.65515350877192646</v>
+        <v>0.6716008771929789</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -2572,8 +2590,8 @@
         <v>0.77083333333333326</v>
       </c>
       <c r="M7" s="15">
-        <f>SUM(F2:F66)</f>
-        <v>8.4444444444444464</v>
+        <f>SUM(F2:F73)</f>
+        <v>8.8194444444444464</v>
       </c>
       <c r="N7">
         <v>180</v>
@@ -2612,7 +2630,7 @@
       </c>
       <c r="M8" s="16">
         <f>TEXT(M7,"[h]")+TEXT(M7,"mm")/60</f>
-        <v>202.66666666666666</v>
+        <v>211.66666666666666</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -2703,7 +2721,7 @@
       </c>
       <c r="J11" s="10">
         <f>SUMIF(Stundenliste[Wer],I11,Stundenliste[Stunden])</f>
-        <v>2.6875</v>
+        <v>2.8124999999999996</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -3838,14 +3856,14 @@
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="23" t="str">
+      <c r="A57" s="2" t="str">
         <f t="shared" ref="A57:A58" si="8">IF(ISNUMBER(B57),LEFT(TEXT(B57,"TTTT"),2)&amp;".","")</f>
         <v>Mi.</v>
       </c>
       <c r="B57" s="3">
         <v>45959</v>
       </c>
-      <c r="C57" s="23" t="s">
+      <c r="C57" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D57" s="4">
@@ -3863,14 +3881,14 @@
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="23" t="str">
+      <c r="A58" s="2" t="str">
         <f t="shared" si="8"/>
         <v>Do.</v>
       </c>
       <c r="B58" s="3">
         <v>45960</v>
       </c>
-      <c r="C58" s="23" t="s">
+      <c r="C58" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D58" s="4">
@@ -3888,14 +3906,14 @@
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="23" t="str">
-        <f>IF(ISNUMBER(B59),LEFT(TEXT(B59,"TTTT"),2)&amp;".","")</f>
+      <c r="A59" s="2" t="str">
+        <f t="shared" ref="A59:A72" si="9">IF(ISNUMBER(B59),LEFT(TEXT(B59,"TTTT"),2)&amp;".","")</f>
         <v>Sa.</v>
       </c>
       <c r="B59" s="3">
         <v>45962</v>
       </c>
-      <c r="C59" s="23" t="s">
+      <c r="C59" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D59" s="4">
@@ -3913,14 +3931,14 @@
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="23" t="str">
-        <f>IF(ISNUMBER(B60),LEFT(TEXT(B60,"TTTT"),2)&amp;".","")</f>
+      <c r="A60" s="2" t="str">
+        <f t="shared" si="9"/>
         <v>So.</v>
       </c>
       <c r="B60" s="3">
         <v>45963</v>
       </c>
-      <c r="C60" s="23" t="s">
+      <c r="C60" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D60" s="4">
@@ -3938,14 +3956,14 @@
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="23" t="str">
-        <f>IF(ISNUMBER(B61),LEFT(TEXT(B61,"TTTT"),2)&amp;".","")</f>
+      <c r="A61" s="2" t="str">
+        <f t="shared" si="9"/>
         <v>Mi.</v>
       </c>
       <c r="B61" s="3">
         <v>45980</v>
       </c>
-      <c r="C61" s="23" t="s">
+      <c r="C61" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D61" s="4">
@@ -3963,14 +3981,14 @@
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="23" t="str">
-        <f>IF(ISNUMBER(B62),LEFT(TEXT(B62,"TTTT"),2)&amp;".","")</f>
+      <c r="A62" s="2" t="str">
+        <f t="shared" si="9"/>
         <v>Do.</v>
       </c>
       <c r="B62" s="3">
         <v>45974</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D62" s="4">
@@ -3988,14 +4006,14 @@
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="23" t="str">
-        <f>IF(ISNUMBER(B63),LEFT(TEXT(B63,"TTTT"),2)&amp;".","")</f>
+      <c r="A63" s="2" t="str">
+        <f t="shared" si="9"/>
         <v>So.</v>
       </c>
       <c r="B63" s="3">
         <v>46082</v>
       </c>
-      <c r="C63" s="23" t="s">
+      <c r="C63" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D63" s="4">
@@ -4013,14 +4031,14 @@
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="23" t="str">
-        <f>IF(ISNUMBER(B64),LEFT(TEXT(B64,"TTTT"),2)&amp;".","")</f>
+      <c r="A64" s="2" t="str">
+        <f t="shared" si="9"/>
         <v>So.</v>
       </c>
       <c r="B64" s="3">
         <v>46082</v>
       </c>
-      <c r="C64" s="23" t="s">
+      <c r="C64" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D64" s="4">
@@ -4038,14 +4056,14 @@
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="23" t="str">
-        <f>IF(ISNUMBER(B65),LEFT(TEXT(B65,"TTTT"),2)&amp;".","")</f>
+      <c r="A65" s="2" t="str">
+        <f t="shared" si="9"/>
         <v>So.</v>
       </c>
       <c r="B65" s="3">
         <v>46082</v>
       </c>
-      <c r="C65" s="23" t="s">
+      <c r="C65" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D65" s="4">
@@ -4063,14 +4081,14 @@
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="23" t="str">
-        <f>IF(ISNUMBER(B66),LEFT(TEXT(B66,"TTTT"),2)&amp;".","")</f>
+      <c r="A66" s="2" t="str">
+        <f t="shared" si="9"/>
         <v>So.</v>
       </c>
       <c r="B66" s="3">
         <v>46082</v>
       </c>
-      <c r="C66" s="23" t="s">
+      <c r="C66" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D66" s="4">
@@ -4086,6 +4104,171 @@
       <c r="G66" s="2" t="s">
         <v>9</v>
       </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>Mo.</v>
+      </c>
+      <c r="B67" s="3">
+        <v>46083</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D67" s="4">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E67" s="4">
+        <v>0.375</v>
+      </c>
+      <c r="F67" s="5">
+        <f>IF(E67&gt;D67,E67-D67,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D67-E67),""))</f>
+        <v>4.1666666666666685E-2</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>Di.</v>
+      </c>
+      <c r="B68" s="3">
+        <v>46084</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D68" s="4">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="E68" s="4">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="F68" s="5">
+        <f>IF(E68&gt;D68,E68-D68,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D68-E68),""))</f>
+        <v>4.166666666666663E-2</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>Mo.</v>
+      </c>
+      <c r="B69" s="3">
+        <v>46083</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D69" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="E69" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F69" s="5">
+        <f>IF(E69&gt;D69,E69-D69,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D69-E69),""))</f>
+        <v>8.333333333333337E-2</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>Di.</v>
+      </c>
+      <c r="B70" s="3">
+        <v>46084</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D70" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="E70" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F70" s="5">
+        <f>IF(E70&gt;D70,E70-D70,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D70-E70),""))</f>
+        <v>8.333333333333337E-2</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>Mi.</v>
+      </c>
+      <c r="B71" s="3">
+        <v>46085</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D71" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="E71" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F71" s="5">
+        <f>IF(E71&gt;D71,E71-D71,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D71-E71),""))</f>
+        <v>8.333333333333337E-2</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>Mi.</v>
+      </c>
+      <c r="B72" s="3">
+        <v>46085</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D72" s="4">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="E72" s="4">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="F72" s="5">
+        <f>IF(E72&gt;D72,E72-D72,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D72-E72),""))</f>
+        <v>4.1666666666666685E-2</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="23" t="str">
+        <f>IF(ISNUMBER(B73),LEFT(TEXT(B73,"TTTT"),2)&amp;".","")</f>
+        <v/>
+      </c>
+      <c r="B73" s="3"/>
+      <c r="C73" s="23"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="5" t="str">
+        <f>IF(E73&gt;D73,E73-D73,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D73-E73),""))</f>
+        <v/>
+      </c>
+      <c r="G73" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -4100,20 +4283,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4261,14 +4444,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A879EED-63D4-4BD6-ABDC-8DEB19CAAEDF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57E083A2-B59E-4178-BBDB-6F72551558F7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -4282,6 +4457,14 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="becce21f-4543-4ee3-84d8-746b4cf7c34b"/>
     <ds:schemaRef ds:uri="d9f85066-e658-4e34-914c-f198c2427564"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A879EED-63D4-4BD6-ABDC-8DEB19CAAEDF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
